--- a/files/港岛-筲箕湾-傲华.xlsx
+++ b/files/港岛-筲箕湾-傲华.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="傲华 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -951,7 +815,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -997,7 +861,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1135,7 +999,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1181,7 +1045,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1319,7 +1183,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1365,7 +1229,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1503,7 +1367,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1549,7 +1413,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1595,7 +1459,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1733,7 +1597,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1779,7 +1643,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1825,7 +1689,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1871,7 +1735,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1917,7 +1781,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -1963,7 +1827,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2009,7 +1873,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2055,7 +1919,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2101,7 +1965,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2147,7 +2011,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2239,7 +2103,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2285,7 +2149,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2331,7 +2195,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2377,7 +2241,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2423,7 +2287,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2469,7 +2333,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2515,7 +2379,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2607,7 +2471,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2653,7 +2517,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2699,7 +2563,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2745,7 +2609,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2791,7 +2655,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2837,7 +2701,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2883,7 +2747,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2929,7 +2793,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3021,7 +2885,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-09</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3067,7 +2931,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3113,7 +2977,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3159,7 +3023,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3205,7 +3069,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3301,7 +3165,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3347,7 +3211,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3393,7 +3257,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-09</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3439,7 +3303,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3485,7 +3349,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3531,7 +3395,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3577,7 +3441,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3623,7 +3487,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3669,7 +3533,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3715,7 +3579,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3761,7 +3625,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-09</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3807,7 +3671,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3899,7 +3763,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -3945,7 +3809,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -3991,7 +3855,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4037,7 +3901,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4083,7 +3947,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4129,7 +3993,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4175,7 +4039,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-16</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -4221,7 +4085,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4267,7 +4131,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-09</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4313,7 +4177,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4359,7 +4223,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4405,7 +4269,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4451,7 +4315,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4497,7 +4361,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4543,7 +4407,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4589,7 +4453,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4635,7 +4499,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -4681,7 +4545,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -4727,7 +4591,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4773,7 +4637,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-16</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4819,7 +4683,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -4865,7 +4729,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -4911,7 +4775,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -4957,7 +4821,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -5003,7 +4867,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5049,7 +4913,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5095,7 +4959,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5141,7 +5005,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5187,7 +5051,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -5233,7 +5097,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5279,7 +5143,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-09</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5325,7 +5189,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -5371,7 +5235,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -5417,7 +5281,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -5463,7 +5327,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -5509,7 +5373,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -5555,7 +5419,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -5601,7 +5465,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -5647,7 +5511,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -5693,7 +5557,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -5739,7 +5603,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -5785,7 +5649,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -5831,7 +5695,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -5877,7 +5741,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -5923,7 +5787,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -5969,7 +5833,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -6015,7 +5879,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -6061,7 +5925,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -6107,7 +5971,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -6153,7 +6017,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -6199,7 +6063,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -6245,7 +6109,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -6291,7 +6155,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-09</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -6337,7 +6201,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -6383,7 +6247,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -6429,7 +6293,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -6475,7 +6339,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -6521,7 +6385,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -6567,7 +6431,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -6613,7 +6477,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -6659,7 +6523,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -6705,7 +6569,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -6751,7 +6615,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -6797,7 +6661,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -6843,7 +6707,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -6889,7 +6753,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -6935,7 +6799,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -6981,7 +6845,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -7027,7 +6891,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -7073,7 +6937,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -7119,7 +6983,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -7165,7 +7029,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -7211,7 +7075,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -7257,7 +7121,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -7303,7 +7167,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-09</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -7349,7 +7213,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -7395,7 +7259,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -7441,7 +7305,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -7487,7 +7351,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -7533,7 +7397,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -7579,7 +7443,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -7625,7 +7489,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -7671,7 +7535,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -7717,7 +7581,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -7763,7 +7627,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -7809,7 +7673,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -7855,7 +7719,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -7877,1543 +7741,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:I25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>傲华 - 傲华 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>156 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>8 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>143 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>5 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 514呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 577呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 737呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 497呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr"/>
-      <c r="H6" s="17" t="inlineStr"/>
-      <c r="I6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 343呎 (1房)
-$776万
-$22,630/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 211呎 (开放式)
-$444万
-$21,043/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 220呎 (开放式)
-$420万
-$19,082/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$867万
-$25,488/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F7" s="19" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$823万
-$25,410/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>F | 456呎 (2房)
-$975万
-$21,382/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>G | 222呎 (开放式)
-$485万
-$21,856/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I7" s="19" t="inlineStr">
-        <is>
-          <t>H | 283呎 (1房)
-$725万
-$25,629/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 342呎 (1房)
-$756万
-$22,114/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 211呎 (开放式)
-$434万
-$20,578/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 220呎 (开放式)
-$414万
-$18,823/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$847万
-$24,924/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F8" s="19" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$812万
-$25,065/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>F | 456呎 (2房)
-$969万
-$21,259/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H8" s="18" t="inlineStr">
-        <is>
-          <t>G | 222呎 (开放式)
-$498万
-$22,441/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I8" s="19" t="inlineStr">
-        <is>
-          <t>H | 283呎 (1房)
-$715万
-$25,272/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 342呎 (1房)
-$682万
-$19,942/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 211呎 (开放式)
-$423万
-$20,062/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 220呎 (开放式)
-$404万
-$18,355/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$784万
-$23,053/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$688万
-$21,241/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>F | 456呎 (2房)
-$946万
-$20,741/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H9" s="18" t="inlineStr">
-        <is>
-          <t>G | 222呎 (开放式)
-$454万
-$20,468/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="I9" s="19" t="inlineStr">
-        <is>
-          <t>H | 283呎 (1房)
-$697万
-$24,636/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 342呎 (1房)
-$665万
-$19,450/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 211呎 (开放式)
-$422万
-$20,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 220呎 (开放式)
-$398万
-$18,109/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$814万
-$23,926/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$679万
-$20,948/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>F | 456呎 (2房)
-$934万
-$20,474/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H10" s="18" t="inlineStr">
-        <is>
-          <t>G | 222呎 (开放式)
-$444万
-$20,018/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I10" s="18" t="inlineStr">
-        <is>
-          <t>H | 283呎 (1房)
-$598万
-$21,117/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 343呎 (1房)
-$656万
-$19,125/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 211呎 (开放式)
-$416万
-$19,697/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 220呎 (开放式)
-$393万
-$17,859/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$698万
-$20,541/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$691万
-$21,336/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>F | 456呎 (2房)
-$920万
-$20,175/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H11" s="18" t="inlineStr">
-        <is>
-          <t>G | 222呎 (开放式)
-$438万
-$19,743/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I11" s="18" t="inlineStr">
-        <is>
-          <t>H | 283呎 (1房)
-$589万
-$20,827/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 342呎 (1房)
-$654万
-$19,123/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 211呎 (开放式)
-$410万
-$19,427/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 220呎 (开放式)
-$388万
-$17,618/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$689万
-$20,259/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$660万
-$20,367/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>F | 456呎 (2房)
-$966万
-$21,189/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H12" s="18" t="inlineStr">
-        <is>
-          <t>G | 222呎 (开放式)
-$441万
-$19,865/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I12" s="18" t="inlineStr">
-        <is>
-          <t>H | 283呎 (1房)
-$581万
-$20,537/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 342呎 (1房)
-$638万
-$18,655/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 211呎 (开放式)
-$404万
-$19,161/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 220呎 (开放式)
-$402万
-$18,250/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$679万
-$19,976/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>F | 456呎 (2房)
-$954万
-$20,914/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H13" s="18" t="inlineStr">
-        <is>
-          <t>G | 221呎 (开放式)
-$426万
-$19,299/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I13" s="18" t="inlineStr">
-        <is>
-          <t>H | 283呎 (1房)
-$573万
-$20,254/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 342呎 (1房)
-$629万
-$18,401/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 211呎 (开放式)
-$399万
-$18,900/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 220呎 (开放式)
-$377万
-$17,145/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$670万
-$19,703/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$642万
-$19,812/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>F | 456呎 (2房)
-$941万
-$20,645/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>G | 221呎 (开放式)
-$425万
-$19,213/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I14" s="18" t="inlineStr">
-        <is>
-          <t>H | 283呎 (1房)
-$565万
-$19,972/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 343呎 (1房)
-$620万
-$18,090/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 211呎 (开放式)
-$394万
-$18,649/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 220呎 (开放式)
-$372万
-$16,918/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$661万
-$19,432/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$633万
-$19,540/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 456呎 (2房)
-$929万
-$20,382/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H15" s="18" t="inlineStr">
-        <is>
-          <t>G | 221呎 (开放式)
-$415万
-$18,783/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I15" s="18" t="inlineStr">
-        <is>
-          <t>H | 283呎 (1房)
-$557万
-$19,696/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 343呎 (1房)
-$612万
-$17,843/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 211呎 (开放式)
-$388万
-$18,393/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 220呎 (开放式)
-$367万
-$16,686/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$652万
-$19,162/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$624万
-$19,272/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 456呎 (2房)
-$918万
-$20,121/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H16" s="18" t="inlineStr">
-        <is>
-          <t>G | 221呎 (开放式)
-$413万
-$18,692/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I16" s="18" t="inlineStr">
-        <is>
-          <t>H | 283呎 (1房)
-$550万
-$19,431/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 343呎 (1房)
-$604万
-$17,595/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 211呎 (开放式)
-$383万
-$18,137/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 220呎 (开放式)
-$362万
-$16,464/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$643万
-$18,900/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$616万
-$19,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 456呎 (2房)
-$922万
-$20,226/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H17" s="18" t="inlineStr">
-        <is>
-          <t>G | 221呎 (开放式)
-$408万
-$18,443/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I17" s="18" t="inlineStr">
-        <is>
-          <t>H | 283呎 (1房)
-$542万
-$19,159/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 343呎 (1房)
-$595万
-$17,353/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 211呎 (开放式)
-$374万
-$17,720/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 220呎 (开放式)
-$353万
-$16,064/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$634万
-$18,632/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$607万
-$18,741/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 456呎 (2房)
-$894万
-$19,607/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H18" s="18" t="inlineStr">
-        <is>
-          <t>G | 221呎 (开放式)
-$398万
-$18,023/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I18" s="18" t="inlineStr">
-        <is>
-          <t>H | 283呎 (1房)
-$535万
-$18,894/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 343呎 (1房)
-$587万
-$17,114/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 211呎 (开放式)
-$372万
-$17,654/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 220呎 (开放式)
-$352万
-$16,018/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$652万
-$19,185/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$599万
-$18,485/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>F | 456呎 (2房)
-$883万
-$19,355/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H19" s="18" t="inlineStr">
-        <is>
-          <t>G | 221呎 (开放式)
-$397万
-$17,950/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I19" s="18" t="inlineStr">
-        <is>
-          <t>H | 283呎 (1房)
-$527万
-$18,633/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 343呎 (1房)
-$580万
-$16,895/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 211呎 (开放式)
-$368万
-$17,431/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 220呎 (开放式)
-$348万
-$15,818/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$617万
-$18,144/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$617万
-$19,046/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>F | 456呎 (2房)
-$871万
-$19,105/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H20" s="18" t="inlineStr">
-        <is>
-          <t>G | 221呎 (开放式)
-$392万
-$17,724/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I20" s="18" t="inlineStr">
-        <is>
-          <t>H | 283呎 (1房)
-$521万
-$18,396/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 342呎 (1房)
-$597万
-$17,462/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 211呎 (开放式)
-$359万
-$17,033/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 220呎 (开放式)
-$340万
-$15,445/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$609万
-$17,912/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$584万
-$18,012/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
-        <is>
-          <t>F | 456呎 (2房)
-$860万
-$18,862/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H21" s="18" t="inlineStr">
-        <is>
-          <t>G | 221呎 (开放式)
-$387万
-$17,507/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I21" s="18" t="inlineStr">
-        <is>
-          <t>H | 283呎 (1房)
-$514万
-$18,163/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 342呎 (1房)
-$565万
-$16,512/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 211呎 (开放式)
-$349万
-$16,559/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 220呎 (开放式)
-$339万
-$15,418/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$601万
-$17,679/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$576万
-$17,778/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>F | 456呎 (2房)
-$849万
-$18,618/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H22" s="18" t="inlineStr">
-        <is>
-          <t>G | 221呎 (开放式)
-$382万
-$17,285/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I22" s="18" t="inlineStr">
-        <is>
-          <t>H | 283呎 (1房)
-$507万
-$17,926/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 343呎 (1房)
-$548万
-$15,968/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 211呎 (开放式)
-$341万
-$16,175/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 220呎 (开放式)
-$335万
-$15,232/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$601万
-$17,682/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$595万
-$18,358/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
-        <is>
-          <t>F | 456呎 (2房)
-$838万
-$18,382/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H23" s="18" t="inlineStr">
-        <is>
-          <t>G | 221呎 (开放式)
-$377万
-$17,068/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I23" s="18" t="inlineStr">
-        <is>
-          <t>H | 283呎 (1房)
-$517万
-$18,279/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 343呎 (1房)
-$548万
-$15,968/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 211呎 (开放式)
-$345万
-$16,355/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 220呎 (开放式)
-$335万
-$15,232/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 340呎 (1房)
-$595万
-$17,491/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>E | 324呎 (1房)
-$570万
-$17,586/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t>F | 456呎 (2房)
-$838万
-$18,382/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H24" s="18" t="inlineStr">
-        <is>
-          <t>G | 222呎 (开放式)
-$377万
-$16,991/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I24" s="18" t="inlineStr">
-        <is>
-          <t>H | 283呎 (1房)
-$501万
-$17,696/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 305呎 (1房)
-$738万
-$24,203/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 190呎 (开放式)
-$393万
-$20,674/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 197呎 (开放式)
-$378万
-$19,173/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 300呎 (1房)
-$679万
-$22,620/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>E | 285呎 (1房)
-$646万
-$22,667/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>F | 417呎 (2房)
-$1,115万
-$26,739/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H25" s="18" t="inlineStr">
-        <is>
-          <t>G | 198呎 (开放式)
-$416万
-$20,985/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I25" s="18" t="inlineStr">
-        <is>
-          <t>H | 246呎 (1房)
-$556万
-$22,585/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-筲箕湾-傲华.xlsx
+++ b/files/港岛-筲箕湾-傲华.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="傲华" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +142,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +223,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +653,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -7741,4 +7920,1543 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>傲华 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 514呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 577呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 737呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 497呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+      <c r="I5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 343呎 (1房)
+$776万
+$22,630/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 211呎 (开放式)
+$444万
+$21,043/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 220呎 (开放式)
+$420万
+$19,082/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$867万
+$25,488/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$823万
+$25,410/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>F | 456呎 (2房)
+$975万
+$21,382/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>G | 222呎 (开放式)
+$485万
+$21,856/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$725万
+$25,629/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 342呎 (1房)
+$756万
+$22,114/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 211呎 (开放式)
+$434万
+$20,578/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 220呎 (开放式)
+$414万
+$18,823/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$847万
+$24,924/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$812万
+$25,065/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>F | 456呎 (2房)
+$969万
+$21,259/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>G | 222呎 (开放式)
+$498万
+$22,441/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I7" s="23" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$715万
+$25,272/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 342呎 (1房)
+$682万
+$19,942/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 211呎 (开放式)
+$423万
+$20,062/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 220呎 (开放式)
+$404万
+$18,355/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$784万
+$23,053/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$688万
+$21,241/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>F | 456呎 (2房)
+$946万
+$20,741/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>G | 222呎 (开放式)
+$454万
+$20,468/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$697万
+$24,636/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 342呎 (1房)
+$665万
+$19,450/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 211呎 (开放式)
+$422万
+$20,000/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 220呎 (开放式)
+$398万
+$18,109/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$814万
+$23,926/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$679万
+$20,948/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 456呎 (2房)
+$934万
+$20,474/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>G | 222呎 (开放式)
+$444万
+$20,018/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$598万
+$21,117/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 343呎 (1房)
+$656万
+$19,125/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 211呎 (开放式)
+$416万
+$19,697/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 220呎 (开放式)
+$393万
+$17,859/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$698万
+$20,541/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$691万
+$21,336/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 456呎 (2房)
+$920万
+$20,175/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>G | 222呎 (开放式)
+$438万
+$19,743/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$589万
+$20,827/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 342呎 (1房)
+$654万
+$19,123/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 211呎 (开放式)
+$410万
+$19,427/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 220呎 (开放式)
+$388万
+$17,618/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$689万
+$20,259/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$660万
+$20,367/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 456呎 (2房)
+$966万
+$21,189/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>G | 222呎 (开放式)
+$441万
+$19,865/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$581万
+$20,537/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 342呎 (1房)
+$638万
+$18,655/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 211呎 (开放式)
+$404万
+$19,161/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 220呎 (开放式)
+$402万
+$18,250/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$679万
+$19,976/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 456呎 (2房)
+$954万
+$20,914/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>G | 221呎 (开放式)
+$426万
+$19,299/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$573万
+$20,254/呎
+(25年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 342呎 (1房)
+$629万
+$18,401/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 211呎 (开放式)
+$399万
+$18,900/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 220呎 (开放式)
+$377万
+$17,145/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$670万
+$19,703/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$642万
+$19,812/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 456呎 (2房)
+$941万
+$20,645/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>G | 221呎 (开放式)
+$425万
+$19,213/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$565万
+$19,972/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 343呎 (1房)
+$620万
+$18,090/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 211呎 (开放式)
+$394万
+$18,649/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 220呎 (开放式)
+$372万
+$16,918/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$661万
+$19,432/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$633万
+$19,540/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 456呎 (2房)
+$929万
+$20,382/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>G | 221呎 (开放式)
+$415万
+$18,783/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$557万
+$19,696/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 343呎 (1房)
+$612万
+$17,843/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 211呎 (开放式)
+$388万
+$18,393/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 220呎 (开放式)
+$367万
+$16,686/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$652万
+$19,162/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$624万
+$19,272/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 456呎 (2房)
+$918万
+$20,121/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>G | 221呎 (开放式)
+$413万
+$18,692/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$550万
+$19,431/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 343呎 (1房)
+$604万
+$17,595/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 211呎 (开放式)
+$383万
+$18,137/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 220呎 (开放式)
+$362万
+$16,464/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$643万
+$18,900/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$616万
+$19,000/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 456呎 (2房)
+$922万
+$20,226/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>G | 221呎 (开放式)
+$408万
+$18,443/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$542万
+$19,159/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 343呎 (1房)
+$595万
+$17,353/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 211呎 (开放式)
+$374万
+$17,720/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 220呎 (开放式)
+$353万
+$16,064/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$634万
+$18,632/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$607万
+$18,741/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 456呎 (2房)
+$894万
+$19,607/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>G | 221呎 (开放式)
+$398万
+$18,023/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="I17" s="22" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$535万
+$18,894/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 343呎 (1房)
+$587万
+$17,114/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 211呎 (开放式)
+$372万
+$17,654/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 220呎 (开放式)
+$352万
+$16,018/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$652万
+$19,185/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$599万
+$18,485/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 456呎 (2房)
+$883万
+$19,355/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>G | 221呎 (开放式)
+$397万
+$17,950/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$527万
+$18,633/呎
+(25年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 343呎 (1房)
+$580万
+$16,895/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 211呎 (开放式)
+$368万
+$17,431/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 220呎 (开放式)
+$348万
+$15,818/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$617万
+$18,144/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$617万
+$19,046/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 456呎 (2房)
+$871万
+$19,105/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>G | 221呎 (开放式)
+$392万
+$17,724/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$521万
+$18,396/呎
+(25年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 342呎 (1房)
+$597万
+$17,462/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 211呎 (开放式)
+$359万
+$17,033/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 220呎 (开放式)
+$340万
+$15,445/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$609万
+$17,912/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$584万
+$18,012/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 456呎 (2房)
+$860万
+$18,862/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>G | 221呎 (开放式)
+$387万
+$17,507/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$514万
+$18,163/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 342呎 (1房)
+$565万
+$16,512/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 211呎 (开放式)
+$349万
+$16,559/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 220呎 (开放式)
+$339万
+$15,418/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$601万
+$17,679/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$576万
+$17,778/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 456呎 (2房)
+$849万
+$18,618/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>G | 221呎 (开放式)
+$382万
+$17,285/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$507万
+$17,926/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 343呎 (1房)
+$548万
+$15,968/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 211呎 (开放式)
+$341万
+$16,175/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 220呎 (开放式)
+$335万
+$15,232/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$601万
+$17,682/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$595万
+$18,358/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 456呎 (2房)
+$838万
+$18,382/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>G | 221呎 (开放式)
+$377万
+$17,068/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$517万
+$18,279/呎
+(25年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 343呎 (1房)
+$548万
+$15,968/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 211呎 (开放式)
+$345万
+$16,355/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 220呎 (开放式)
+$335万
+$15,232/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 340呎 (1房)
+$595万
+$17,491/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 324呎 (1房)
+$570万
+$17,586/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>F | 456呎 (2房)
+$838万
+$18,382/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>G | 222呎 (开放式)
+$377万
+$16,991/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$501万
+$17,696/呎
+(25年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 305呎 (1房)
+$738万
+$24,203/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 190呎 (开放式)
+$393万
+$20,674/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 197呎 (开放式)
+$378万
+$19,173/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 300呎 (1房)
+$679万
+$22,620/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 285呎 (1房)
+$646万
+$22,667/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 417呎 (2房)
+$1115万
+$26,739/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>G | 198呎 (开放式)
+$416万
+$20,985/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>H | 246呎 (1房)
+$556万
+$22,585/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-筲箕湾-傲华.xlsx
+++ b/files/港岛-筲箕湾-傲华.xlsx
@@ -653,7 +653,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-筲箕湾-傲华.xlsx
+++ b/files/港岛-筲箕湾-傲华.xlsx
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J158"/>
+  <dimension ref="A1:N158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -656,6 +656,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -713,6 +717,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -763,6 +787,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -813,6 +857,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -863,6 +927,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -913,6 +997,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -959,6 +1063,22 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>6382640</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>22553</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1005,6 +1125,22 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>4852000</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>21856</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1051,6 +1187,22 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>9750000</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>21382</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1097,6 +1249,22 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>7245040</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>22361</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1143,6 +1311,22 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>7626080</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>22430</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1189,6 +1373,22 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>4198000</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>19082</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1235,6 +1435,22 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>4440000</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>21043</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1281,6 +1497,22 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>7762000</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>22630</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1327,6 +1559,22 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>6293760</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>22239</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1373,6 +1621,22 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>4982000</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>22441</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1419,6 +1683,22 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>9694000</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>21259</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1465,6 +1745,22 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>7146480</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>22057</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1511,6 +1807,22 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>7457120</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>21933</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1557,6 +1869,22 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>4141000</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>18823</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1603,6 +1931,22 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>4342000</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>20578</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1649,6 +1993,22 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>7563000</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>22114</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1695,6 +2055,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>6135360</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>21680</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1741,6 +2117,22 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>4544000</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>20468</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1787,6 +2179,22 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>9458000</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>20741</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1833,6 +2241,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>6882000</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>21241</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1879,6 +2303,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>7838000</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>23053</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1925,6 +2365,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>4038000</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>18355</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1971,6 +2427,22 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>4233000</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>20062</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2017,6 +2489,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>6820000</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>19942</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2063,6 +2551,22 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>5976000</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>21117</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2109,6 +2613,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>4444000</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>20018</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2155,6 +2675,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>9336000</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>20474</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2201,6 +2737,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>6787000</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>20948</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2247,6 +2799,22 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>7158800</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>21055</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2293,6 +2861,22 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>3984000</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>18109</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2339,6 +2923,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>4220000</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2385,6 +2985,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>6652000</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>19450</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2431,6 +3047,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>5894000</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>20827</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2477,6 +3109,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>4383000</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>19743</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2523,6 +3171,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>9200000</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>20175</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2569,6 +3233,22 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>6913000</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>21336</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2615,6 +3295,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>6984000</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>20541</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2661,6 +3357,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>3929000</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>17859</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2707,6 +3419,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>4156000</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>19697</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2753,6 +3481,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>6560000</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>19125</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2799,6 +3543,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>5812000</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>20537</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2845,6 +3605,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>4410000</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>19865</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2891,6 +3667,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>9662000</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>21189</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2937,6 +3729,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>6599000</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>20367</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2983,6 +3791,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>6888000</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>20259</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3029,6 +3853,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>3876000</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>17618</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3075,6 +3915,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>4099000</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>19427</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3121,6 +3977,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>6540000</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>19123</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3167,6 +4039,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>5732000</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>20254</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3213,6 +4101,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>4265000</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>19299</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3259,6 +4163,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>9537000</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>20914</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3309,6 +4229,26 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3355,6 +4295,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>6792000</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>19976</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3401,6 +4357,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>4015000</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>18250</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3447,6 +4419,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>4043000</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>19161</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3493,6 +4481,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>6380000</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>18655</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3539,6 +4543,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>5652000</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>19972</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3585,6 +4605,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>4246000</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>19213</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3631,6 +4667,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>9414000</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>20645</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3677,6 +4729,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>6419000</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>19812</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3723,6 +4791,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>6699000</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>19703</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3769,6 +4853,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>3772000</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>17145</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3815,6 +4915,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>3988000</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>18900</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3861,6 +4977,22 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>6293000</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>18401</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3907,6 +5039,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>5574000</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>19696</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3953,6 +5101,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>4151000</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>18783</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3999,6 +5163,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>9294000</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>20382</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4045,6 +5225,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>6331000</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>19540</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4091,6 +5287,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>6607000</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>19432</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4137,6 +5349,22 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>3722000</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>16918</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4183,6 +5411,22 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>3935000</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>18649</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4229,6 +5473,22 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>6205000</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>18090</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4275,6 +5535,22 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>5499000</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>19431</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4321,6 +5597,22 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>4131000</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>18692</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4367,6 +5659,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>9175000</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>20121</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4413,6 +5721,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>6244000</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>19272</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4459,6 +5783,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>6515000</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>19162</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4505,6 +5845,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>3671000</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>16686</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4551,6 +5907,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>3881000</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>18393</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4597,6 +5969,22 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>6120000</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>17843</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4643,6 +6031,22 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>5422000</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>19159</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4689,6 +6093,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>4076000</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>18443</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4735,6 +6155,22 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>9223000</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>20226</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4781,6 +6217,22 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>6156000</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>19000</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4827,6 +6279,22 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>6426000</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>18900</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4873,6 +6341,22 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>3622000</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>16464</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4919,6 +6403,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>3827000</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>18137</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4965,6 +6465,22 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>6035000</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>17595</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5011,6 +6527,22 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>5347000</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>18894</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5057,6 +6589,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>3983000</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>18023</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5103,6 +6651,22 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>8941000</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>19607</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5149,6 +6713,22 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>6072000</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>18741</v>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5195,6 +6775,22 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>6335000</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>18632</v>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5241,6 +6837,22 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>3534000</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>16064</v>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5287,6 +6899,22 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>3739000</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>17720</v>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5333,6 +6961,22 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>5952000</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>17353</v>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5379,6 +7023,22 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>5273000</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>18633</v>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5425,6 +7085,22 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>3967000</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>17950</v>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5471,6 +7147,22 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>8826000</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>19355</v>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5517,6 +7209,22 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>5989000</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>18485</v>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5563,6 +7271,22 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>6523000</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>19185</v>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5609,6 +7333,22 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>3524000</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>16018</v>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5655,6 +7395,22 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>3725000</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>17654</v>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5701,6 +7457,22 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>5870000</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>17114</v>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5747,6 +7519,22 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>5206000</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>18396</v>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5793,6 +7581,22 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>3917000</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>17724</v>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5839,6 +7643,22 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>8712000</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>19105</v>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5885,6 +7705,22 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>6171000</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>19046</v>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5931,6 +7767,22 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>6169000</v>
+      </c>
+      <c r="L115" s="5" t="n">
+        <v>18144</v>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5977,6 +7829,22 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>3480000</v>
+      </c>
+      <c r="L116" s="5" t="n">
+        <v>15818</v>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6023,6 +7891,22 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>3678000</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>17431</v>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6069,6 +7953,22 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>5795000</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>16895</v>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6115,6 +8015,22 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>5140000</v>
+      </c>
+      <c r="L119" s="5" t="n">
+        <v>18163</v>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6161,6 +8077,22 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>3869000</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>17507</v>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6207,6 +8139,22 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>8601000</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>18862</v>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6253,6 +8201,22 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>5836000</v>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>18012</v>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6299,6 +8263,22 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>6090000</v>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>17912</v>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6345,6 +8325,22 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>3398000</v>
+      </c>
+      <c r="L124" s="5" t="n">
+        <v>15445</v>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6391,6 +8387,22 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="n">
+        <v>3594000</v>
+      </c>
+      <c r="L125" s="5" t="n">
+        <v>17033</v>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6437,6 +8449,22 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>5972000</v>
+      </c>
+      <c r="L126" s="5" t="n">
+        <v>17462</v>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6483,6 +8511,22 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="n">
+        <v>5073000</v>
+      </c>
+      <c r="L127" s="5" t="n">
+        <v>17926</v>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6529,6 +8573,22 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="n">
+        <v>3820000</v>
+      </c>
+      <c r="L128" s="5" t="n">
+        <v>17285</v>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6575,6 +8635,22 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>8490000</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>18618</v>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6621,6 +8697,22 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="n">
+        <v>5760000</v>
+      </c>
+      <c r="L130" s="5" t="n">
+        <v>17778</v>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6667,6 +8759,22 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="n">
+        <v>6011000</v>
+      </c>
+      <c r="L131" s="5" t="n">
+        <v>17679</v>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6713,6 +8821,22 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>3392000</v>
+      </c>
+      <c r="L132" s="5" t="n">
+        <v>15418</v>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6759,6 +8883,22 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>3494000</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>16559</v>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6805,6 +8945,22 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="n">
+        <v>5647000</v>
+      </c>
+      <c r="L134" s="5" t="n">
+        <v>16512</v>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6851,6 +9007,22 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="n">
+        <v>5173000</v>
+      </c>
+      <c r="L135" s="5" t="n">
+        <v>18279</v>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6897,6 +9069,22 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="n">
+        <v>3772000</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>17068</v>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6943,6 +9131,22 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="n">
+        <v>8382000</v>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>18382</v>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6989,6 +9193,22 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>5948000</v>
+      </c>
+      <c r="L138" s="5" t="n">
+        <v>18358</v>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7035,6 +9255,22 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="n">
+        <v>6012000</v>
+      </c>
+      <c r="L139" s="5" t="n">
+        <v>17682</v>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7081,6 +9317,22 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>3351000</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>15232</v>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7127,6 +9379,22 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="n">
+        <v>3413000</v>
+      </c>
+      <c r="L141" s="5" t="n">
+        <v>16175</v>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7173,6 +9441,22 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="n">
+        <v>5477000</v>
+      </c>
+      <c r="L142" s="5" t="n">
+        <v>15968</v>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7219,6 +9503,22 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="n">
+        <v>5008000</v>
+      </c>
+      <c r="L143" s="5" t="n">
+        <v>17696</v>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7265,6 +9565,22 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="5" t="n">
+        <v>3772000</v>
+      </c>
+      <c r="L144" s="5" t="n">
+        <v>16991</v>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7311,6 +9627,22 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="n">
+        <v>8382000</v>
+      </c>
+      <c r="L145" s="5" t="n">
+        <v>18382</v>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7357,6 +9689,22 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>5698000</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>17586</v>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7403,6 +9751,22 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="5" t="n">
+        <v>5947000</v>
+      </c>
+      <c r="L147" s="5" t="n">
+        <v>17491</v>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7449,6 +9813,22 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="n">
+        <v>3351000</v>
+      </c>
+      <c r="L148" s="5" t="n">
+        <v>15232</v>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7495,6 +9875,22 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>3451000</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <v>16355</v>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7541,6 +9937,22 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>5477000</v>
+      </c>
+      <c r="L150" s="5" t="n">
+        <v>15968</v>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7587,6 +9999,22 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="n">
+        <v>5556000</v>
+      </c>
+      <c r="L151" s="5" t="n">
+        <v>22585</v>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7633,6 +10061,22 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="n">
+        <v>4155000</v>
+      </c>
+      <c r="L152" s="5" t="n">
+        <v>20985</v>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7679,6 +10123,22 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="n">
+        <v>11150000</v>
+      </c>
+      <c r="L153" s="5" t="n">
+        <v>26739</v>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7725,6 +10185,22 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="n">
+        <v>6460000</v>
+      </c>
+      <c r="L154" s="5" t="n">
+        <v>22667</v>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7771,6 +10247,22 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="n">
+        <v>6786000</v>
+      </c>
+      <c r="L155" s="5" t="n">
+        <v>22620</v>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7817,6 +10309,22 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="n">
+        <v>3777000</v>
+      </c>
+      <c r="L156" s="5" t="n">
+        <v>19173</v>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7863,6 +10371,22 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="n">
+        <v>3928000</v>
+      </c>
+      <c r="L157" s="5" t="n">
+        <v>20674</v>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7909,13 +10433,29 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="5" t="n">
+        <v>7382000</v>
+      </c>
+      <c r="L158" s="5" t="n">
+        <v>24203</v>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -8114,7 +10654,7 @@
           <t>A | 343呎 (1房)
 $776万
 $22,630/呎
-(26年-06月)</t>
+(26年-06月-19日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -8122,7 +10662,7 @@
           <t>B | 211呎 (开放式)
 $444万
 $21,043/呎
-(25年-06月)</t>
+(25年-06月-01日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -8130,7 +10670,7 @@
           <t>C | 220呎 (开放式)
 $420万
 $19,082/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -8154,7 +10694,7 @@
           <t>F | 456呎 (2房)
 $975万
 $21,382/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
@@ -8162,7 +10702,7 @@
           <t>G | 222呎 (开放式)
 $485万
 $21,856/呎
-(26年-01月)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr">
@@ -8185,7 +10725,7 @@
           <t>A | 342呎 (1房)
 $756万
 $22,114/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -8193,7 +10733,7 @@
           <t>B | 211呎 (开放式)
 $434万
 $20,578/呎
-(25年-04月)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -8201,7 +10741,7 @@
           <t>C | 220呎 (开放式)
 $414万
 $18,823/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
@@ -8225,7 +10765,7 @@
           <t>F | 456呎 (2房)
 $969万
 $21,259/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="H7" s="22" t="inlineStr">
@@ -8233,7 +10773,7 @@
           <t>G | 222呎 (开放式)
 $498万
 $22,441/呎
-(26年-01月)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="I7" s="23" t="inlineStr">
@@ -8256,7 +10796,7 @@
           <t>A | 342呎 (1房)
 $682万
 $19,942/呎
-(25年-12月)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -8264,7 +10804,7 @@
           <t>B | 211呎 (开放式)
 $423万
 $20,062/呎
-(25年-03月)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -8272,7 +10812,7 @@
           <t>C | 220呎 (开放式)
 $404万
 $18,355/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -8280,7 +10820,7 @@
           <t>D | 340呎 (1房)
 $784万
 $23,053/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -8288,7 +10828,7 @@
           <t>E | 324呎 (1房)
 $688万
 $21,241/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -8296,7 +10836,7 @@
           <t>F | 456呎 (2房)
 $946万
 $20,741/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
@@ -8304,7 +10844,7 @@
           <t>G | 222呎 (开放式)
 $454万
 $20,468/呎
-(25年-11月)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="I8" s="23" t="inlineStr">
@@ -8327,7 +10867,7 @@
           <t>A | 342呎 (1房)
 $665万
 $19,450/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -8335,7 +10875,7 @@
           <t>B | 211呎 (开放式)
 $422万
 $20,000/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -8343,7 +10883,7 @@
           <t>C | 220呎 (开放式)
 $398万
 $18,109/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -8359,7 +10899,7 @@
           <t>E | 324呎 (1房)
 $679万
 $20,948/呎
-(25年-10月)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -8367,7 +10907,7 @@
           <t>F | 456呎 (2房)
 $934万
 $20,474/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
@@ -8375,7 +10915,7 @@
           <t>G | 222呎 (开放式)
 $444万
 $20,018/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -8383,7 +10923,7 @@
           <t>H | 283呎 (1房)
 $598万
 $21,117/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
     </row>
@@ -8398,7 +10938,7 @@
           <t>A | 343呎 (1房)
 $656万
 $19,125/呎
-(25年-05月)</t>
+(25年-05月-14日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -8406,7 +10946,7 @@
           <t>B | 211呎 (开放式)
 $416万
 $19,697/呎
-(25年-02月)</t>
+(25年-02月-18日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -8414,7 +10954,7 @@
           <t>C | 220呎 (开放式)
 $393万
 $17,859/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -8422,7 +10962,7 @@
           <t>D | 340呎 (1房)
 $698万
 $20,541/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -8430,7 +10970,7 @@
           <t>E | 324呎 (1房)
 $691万
 $21,336/呎
-(25年-11月)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -8438,7 +10978,7 @@
           <t>F | 456呎 (2房)
 $920万
 $20,175/呎
-(26年-02月)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
@@ -8446,7 +10986,7 @@
           <t>G | 222呎 (开放式)
 $438万
 $19,743/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -8454,7 +10994,7 @@
           <t>H | 283呎 (1房)
 $589万
 $20,827/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
     </row>
@@ -8469,7 +11009,7 @@
           <t>A | 342呎 (1房)
 $654万
 $19,123/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -8477,7 +11017,7 @@
           <t>B | 211呎 (开放式)
 $410万
 $19,427/呎
-(25年-02月)</t>
+(25年-02月-09日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -8485,7 +11025,7 @@
           <t>C | 220呎 (开放式)
 $388万
 $17,618/呎
-(25年-01月)</t>
+(25年-01月-07日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -8493,7 +11033,7 @@
           <t>D | 340呎 (1房)
 $689万
 $20,259/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -8501,7 +11041,7 @@
           <t>E | 324呎 (1房)
 $660万
 $20,367/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -8509,7 +11049,7 @@
           <t>F | 456呎 (2房)
 $966万
 $21,189/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -8517,7 +11057,7 @@
           <t>G | 222呎 (开放式)
 $441万
 $19,865/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -8525,7 +11065,7 @@
           <t>H | 283呎 (1房)
 $581万
 $20,537/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -8540,7 +11080,7 @@
           <t>A | 342呎 (1房)
 $638万
 $18,655/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -8548,7 +11088,7 @@
           <t>B | 211呎 (开放式)
 $404万
 $19,161/呎
-(25年-02月)</t>
+(25年-02月-09日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -8556,7 +11096,7 @@
           <t>C | 220呎 (开放式)
 $402万
 $18,250/呎
-(25年-02月)</t>
+(25年-02月-24日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -8564,7 +11104,7 @@
           <t>D | 340呎 (1房)
 $679万
 $19,976/呎
-(25年-10月)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -8580,7 +11120,7 @@
           <t>F | 456呎 (2房)
 $954万
 $20,914/呎
-(25年-10月)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -8588,7 +11128,7 @@
           <t>G | 221呎 (开放式)
 $426万
 $19,299/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -8596,7 +11136,7 @@
           <t>H | 283呎 (1房)
 $573万
 $20,254/呎
-(25年-04月)</t>
+(25年-04月-06日)</t>
         </is>
       </c>
     </row>
@@ -8611,7 +11151,7 @@
           <t>A | 342呎 (1房)
 $629万
 $18,401/呎
-(25年-08月)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -8619,7 +11159,7 @@
           <t>B | 211呎 (开放式)
 $399万
 $18,900/呎
-(25年-02月)</t>
+(25年-02月-09日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -8627,7 +11167,7 @@
           <t>C | 220呎 (开放式)
 $377万
 $17,145/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -8635,7 +11175,7 @@
           <t>D | 340呎 (1房)
 $670万
 $19,703/呎
-(25年-10月)</t>
+(25年-10月-29日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -8643,7 +11183,7 @@
           <t>E | 324呎 (1房)
 $642万
 $19,812/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -8651,7 +11191,7 @@
           <t>F | 456呎 (2房)
 $941万
 $20,645/呎
-(25年-10月)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -8659,7 +11199,7 @@
           <t>G | 221呎 (开放式)
 $425万
 $19,213/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
@@ -8667,7 +11207,7 @@
           <t>H | 283呎 (1房)
 $565万
 $19,972/呎
-(25年-10月)</t>
+(25年-10月-29日)</t>
         </is>
       </c>
     </row>
@@ -8682,7 +11222,7 @@
           <t>A | 343呎 (1房)
 $620万
 $18,090/呎
-(25年-02月)</t>
+(25年-02月-16日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -8690,7 +11230,7 @@
           <t>B | 211呎 (开放式)
 $394万
 $18,649/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -8698,7 +11238,7 @@
           <t>C | 220呎 (开放式)
 $372万
 $16,918/呎
-(25年-01月)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -8706,7 +11246,7 @@
           <t>D | 340呎 (1房)
 $661万
 $19,432/呎
-(25年-08月)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -8714,7 +11254,7 @@
           <t>E | 324呎 (1房)
 $633万
 $19,540/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -8722,7 +11262,7 @@
           <t>F | 456呎 (2房)
 $929万
 $20,382/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -8730,7 +11270,7 @@
           <t>G | 221呎 (开放式)
 $415万
 $18,783/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -8738,7 +11278,7 @@
           <t>H | 283呎 (1房)
 $557万
 $19,696/呎
-(25年-06月)</t>
+(25年-06月-07日)</t>
         </is>
       </c>
     </row>
@@ -8753,7 +11293,7 @@
           <t>A | 343呎 (1房)
 $612万
 $17,843/呎
-(25年-02月)</t>
+(25年-02月-04日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -8761,7 +11301,7 @@
           <t>B | 211呎 (开放式)
 $388万
 $18,393/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -8769,7 +11309,7 @@
           <t>C | 220呎 (开放式)
 $367万
 $16,686/呎
-(25年-02月)</t>
+(25年-02月-04日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -8777,7 +11317,7 @@
           <t>D | 340呎 (1房)
 $652万
 $19,162/呎
-(25年-04月)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -8785,7 +11325,7 @@
           <t>E | 324呎 (1房)
 $624万
 $19,272/呎
-(25年-01月)</t>
+(25年-01月-23日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -8793,7 +11333,7 @@
           <t>F | 456呎 (2房)
 $918万
 $20,121/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -8801,7 +11341,7 @@
           <t>G | 221呎 (开放式)
 $413万
 $18,692/呎
-(25年-02月)</t>
+(25年-02月-09日)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -8809,7 +11349,7 @@
           <t>H | 283呎 (1房)
 $550万
 $19,431/呎
-(25年-05月)</t>
+(25年-05月-13日)</t>
         </is>
       </c>
     </row>
@@ -8824,7 +11364,7 @@
           <t>A | 343呎 (1房)
 $604万
 $17,595/呎
-(25年-02月)</t>
+(25年-02月-04日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -8832,7 +11372,7 @@
           <t>B | 211呎 (开放式)
 $383万
 $18,137/呎
-(25年-02月)</t>
+(25年-02月-04日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -8840,7 +11380,7 @@
           <t>C | 220呎 (开放式)
 $362万
 $16,464/呎
-(25年-01月)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -8848,7 +11388,7 @@
           <t>D | 340呎 (1房)
 $643万
 $18,900/呎
-(25年-02月)</t>
+(25年-02月-16日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -8856,7 +11396,7 @@
           <t>E | 324呎 (1房)
 $616万
 $19,000/呎
-(25年-02月)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -8864,7 +11404,7 @@
           <t>F | 456呎 (2房)
 $922万
 $20,226/呎
-(25年-11月)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -8872,7 +11412,7 @@
           <t>G | 221呎 (开放式)
 $408万
 $18,443/呎
-(25年-05月)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -8880,7 +11420,7 @@
           <t>H | 283呎 (1房)
 $542万
 $19,159/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
     </row>
@@ -8895,7 +11435,7 @@
           <t>A | 343呎 (1房)
 $595万
 $17,353/呎
-(25年-02月)</t>
+(25年-02月-09日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -8903,7 +11443,7 @@
           <t>B | 211呎 (开放式)
 $374万
 $17,720/呎
-(25年-01月)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -8911,7 +11451,7 @@
           <t>C | 220呎 (开放式)
 $353万
 $16,064/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -8919,7 +11459,7 @@
           <t>D | 340呎 (1房)
 $634万
 $18,632/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -8927,7 +11467,7 @@
           <t>E | 324呎 (1房)
 $607万
 $18,741/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -8935,7 +11475,7 @@
           <t>F | 456呎 (2房)
 $894万
 $19,607/呎
-(25年-06月)</t>
+(25年-06月-01日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -8943,7 +11483,7 @@
           <t>G | 221呎 (开放式)
 $398万
 $18,023/呎
-(25年-04月)</t>
+(25年-04月-06日)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -8951,7 +11491,7 @@
           <t>H | 283呎 (1房)
 $535万
 $18,894/呎
-(25年-03月)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
     </row>
@@ -8966,7 +11506,7 @@
           <t>A | 343呎 (1房)
 $587万
 $17,114/呎
-(25年-01月)</t>
+(25年-01月-23日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -8974,7 +11514,7 @@
           <t>B | 211呎 (开放式)
 $372万
 $17,654/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -8982,7 +11522,7 @@
           <t>C | 220呎 (开放式)
 $352万
 $16,018/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -8990,7 +11530,7 @@
           <t>D | 340呎 (1房)
 $652万
 $19,185/呎
-(25年-02月)</t>
+(25年-02月-17日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -8998,7 +11538,7 @@
           <t>E | 324呎 (1房)
 $599万
 $18,485/呎
-(25年-02月)</t>
+(25年-02月-03日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -9006,7 +11546,7 @@
           <t>F | 456呎 (2房)
 $883万
 $19,355/呎
-(25年-05月)</t>
+(25年-05月-01日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -9014,7 +11554,7 @@
           <t>G | 221呎 (开放式)
 $397万
 $17,950/呎
-(25年-02月)</t>
+(25年-02月-20日)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -9022,7 +11562,7 @@
           <t>H | 283呎 (1房)
 $527万
 $18,633/呎
-(25年-01月)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
     </row>
@@ -9037,7 +11577,7 @@
           <t>A | 343呎 (1房)
 $580万
 $16,895/呎
-(25年-02月)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -9045,7 +11585,7 @@
           <t>B | 211呎 (开放式)
 $368万
 $17,431/呎
-(25年-01月)</t>
+(25年-01月-23日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -9053,7 +11593,7 @@
           <t>C | 220呎 (开放式)
 $348万
 $15,818/呎
-(25年-01月)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -9061,7 +11601,7 @@
           <t>D | 340呎 (1房)
 $617万
 $18,144/呎
-(25年-01月)</t>
+(25年-01月-22日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -9069,7 +11609,7 @@
           <t>E | 324呎 (1房)
 $617万
 $19,046/呎
-(25年-02月)</t>
+(25年-02月-04日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -9077,7 +11617,7 @@
           <t>F | 456呎 (2房)
 $871万
 $19,105/呎
-(25年-08月)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -9085,7 +11625,7 @@
           <t>G | 221呎 (开放式)
 $392万
 $17,724/呎
-(25年-02月)</t>
+(25年-02月-26日)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -9093,7 +11633,7 @@
           <t>H | 283呎 (1房)
 $521万
 $18,396/呎
-(25年-02月)</t>
+(25年-02月-02日)</t>
         </is>
       </c>
     </row>
@@ -9108,7 +11648,7 @@
           <t>A | 342呎 (1房)
 $597万
 $17,462/呎
-(25年-02月)</t>
+(25年-02月-02日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -9116,7 +11656,7 @@
           <t>B | 211呎 (开放式)
 $359万
 $17,033/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -9124,7 +11664,7 @@
           <t>C | 220呎 (开放式)
 $340万
 $15,445/呎
-(25年-02月)</t>
+(25年-02月-09日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -9132,7 +11672,7 @@
           <t>D | 340呎 (1房)
 $609万
 $17,912/呎
-(25年-01月)</t>
+(25年-01月-23日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -9140,7 +11680,7 @@
           <t>E | 324呎 (1房)
 $584万
 $18,012/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -9148,7 +11688,7 @@
           <t>F | 456呎 (2房)
 $860万
 $18,862/呎
-(25年-08月)</t>
+(25年-08月-05日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -9156,7 +11696,7 @@
           <t>G | 221呎 (开放式)
 $387万
 $17,507/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -9164,7 +11704,7 @@
           <t>H | 283呎 (1房)
 $514万
 $18,163/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
     </row>
@@ -9179,7 +11719,7 @@
           <t>A | 342呎 (1房)
 $565万
 $16,512/呎
-(25年-02月)</t>
+(25年-02月-02日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -9187,7 +11727,7 @@
           <t>B | 211呎 (开放式)
 $349万
 $16,559/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -9195,7 +11735,7 @@
           <t>C | 220呎 (开放式)
 $339万
 $15,418/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -9203,7 +11743,7 @@
           <t>D | 340呎 (1房)
 $601万
 $17,679/呎
-(25年-02月)</t>
+(25年-02月-02日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -9211,7 +11751,7 @@
           <t>E | 324呎 (1房)
 $576万
 $17,778/呎
-(25年-01月)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -9219,7 +11759,7 @@
           <t>F | 456呎 (2房)
 $849万
 $18,618/呎
-(25年-07月)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -9227,7 +11767,7 @@
           <t>G | 221呎 (开放式)
 $382万
 $17,285/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -9235,7 +11775,7 @@
           <t>H | 283呎 (1房)
 $507万
 $17,926/呎
-(25年-03月)</t>
+(25年-03月-13日)</t>
         </is>
       </c>
     </row>
@@ -9250,7 +11790,7 @@
           <t>A | 343呎 (1房)
 $548万
 $15,968/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -9258,7 +11798,7 @@
           <t>B | 211呎 (开放式)
 $341万
 $16,175/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -9266,7 +11806,7 @@
           <t>C | 220呎 (开放式)
 $335万
 $15,232/呎
-(25年-02月)</t>
+(25年-02月-03日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -9274,7 +11814,7 @@
           <t>D | 340呎 (1房)
 $601万
 $17,682/呎
-(25年-02月)</t>
+(25年-02月-05日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -9282,7 +11822,7 @@
           <t>E | 324呎 (1房)
 $595万
 $18,358/呎
-(25年-01月)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -9290,7 +11830,7 @@
           <t>F | 456呎 (2房)
 $838万
 $18,382/呎
-(25年-05月)</t>
+(25年-05月-13日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -9298,7 +11838,7 @@
           <t>G | 221呎 (开放式)
 $377万
 $17,068/呎
-(25年-02月)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -9306,7 +11846,7 @@
           <t>H | 283呎 (1房)
 $517万
 $18,279/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
     </row>
@@ -9321,7 +11861,7 @@
           <t>A | 343呎 (1房)
 $548万
 $15,968/呎
-(25年-02月)</t>
+(25年-02月-03日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -9329,7 +11869,7 @@
           <t>B | 211呎 (开放式)
 $345万
 $16,355/呎
-(25年-02月)</t>
+(25年-02月-03日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -9337,7 +11877,7 @@
           <t>C | 220呎 (开放式)
 $335万
 $15,232/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -9345,7 +11885,7 @@
           <t>D | 340呎 (1房)
 $595万
 $17,491/呎
-(25年-02月)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -9353,7 +11893,7 @@
           <t>E | 324呎 (1房)
 $570万
 $17,586/呎
-(25年-02月)</t>
+(25年-02月-09日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -9361,7 +11901,7 @@
           <t>F | 456呎 (2房)
 $838万
 $18,382/呎
-(25年-06月)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -9369,7 +11909,7 @@
           <t>G | 222呎 (开放式)
 $377万
 $16,991/呎
-(25年-02月)</t>
+(25年-02月-17日)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -9377,7 +11917,7 @@
           <t>H | 283呎 (1房)
 $501万
 $17,696/呎
-(25年-02月)</t>
+(25年-02月-17日)</t>
         </is>
       </c>
     </row>
@@ -9392,7 +11932,7 @@
           <t>A | 305呎 (1房)
 $738万
 $24,203/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -9400,7 +11940,7 @@
           <t>B | 190呎 (开放式)
 $393万
 $20,674/呎
-(25年-05月)</t>
+(25年-05月-12日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -9408,7 +11948,7 @@
           <t>C | 197呎 (开放式)
 $378万
 $19,173/呎
-(25年-05月)</t>
+(25年-05月-13日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -9416,7 +11956,7 @@
           <t>D | 300呎 (1房)
 $679万
 $22,620/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -9424,7 +11964,7 @@
           <t>E | 285呎 (1房)
 $646万
 $22,667/呎
-(25年-08月)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -9432,7 +11972,7 @@
           <t>F | 417呎 (2房)
 $1115万
 $26,739/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -9440,7 +11980,7 @@
           <t>G | 198呎 (开放式)
 $416万
 $20,985/呎
-(25年-05月)</t>
+(25年-05月-26日)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -9448,7 +11988,7 @@
           <t>H | 246呎 (1房)
 $556万
 $22,585/呎
-(25年-05月)</t>
+(25年-05月-01日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-筲箕湾-傲华.xlsx
+++ b/files/港岛-筲箕湾-傲华.xlsx
@@ -1063,14 +1063,14 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>6382640</v>
+        <v>6890350</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>22553</v>
+        <v>24348</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -1249,14 +1249,14 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>7245040</v>
+        <v>7821350</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>22361</v>
+        <v>24140</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
@@ -1311,14 +1311,14 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>7626080</v>
+        <v>8232700</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>22430</v>
+        <v>24214</v>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
@@ -1559,14 +1559,14 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>6293760</v>
+        <v>6794400</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>22239</v>
+        <v>24008</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
@@ -1745,14 +1745,14 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>7146480</v>
+        <v>7714950</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>22057</v>
+        <v>23812</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
@@ -1807,14 +1807,14 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>7457120</v>
+        <v>8050300</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>21933</v>
+        <v>23677</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
@@ -2055,14 +2055,14 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>6135360</v>
+        <v>6623400</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>21680</v>
+        <v>23404</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
@@ -2799,18 +2799,18 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="K35" s="5" t="n">
-        <v>7158800</v>
+        <v>7728250</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>21055</v>
+        <v>22730</v>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>180天醫護專業付款計劃</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">

--- a/files/港岛-筲箕湾-傲华.xlsx
+++ b/files/港岛-筲箕湾-傲华.xlsx
@@ -10654,7 +10654,7 @@
           <t>A | 343呎 (1房)
 $776万
 $22,630/呎
-(26年-06月-19日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -10662,7 +10662,7 @@
           <t>B | 211呎 (开放式)
 $444万
 $21,043/呎
-(25年-06月-01日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -10670,7 +10670,7 @@
           <t>C | 220呎 (开放式)
 $420万
 $19,082/呎
-(25年-01月-26日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -10694,7 +10694,7 @@
           <t>F | 456呎 (2房)
 $975万
 $21,382/呎
-(26年-02月-08日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
@@ -10702,7 +10702,7 @@
           <t>G | 222呎 (开放式)
 $485万
 $21,856/呎
-(26年-01月-21日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr">
@@ -10725,7 +10725,7 @@
           <t>A | 342呎 (1房)
 $756万
 $22,114/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -10733,7 +10733,7 @@
           <t>B | 211呎 (开放式)
 $434万
 $20,578/呎
-(25年-04月-08日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -10741,7 +10741,7 @@
           <t>C | 220呎 (开放式)
 $414万
 $18,823/呎
-(25年-02月-06日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
@@ -10765,7 +10765,7 @@
           <t>F | 456呎 (2房)
 $969万
 $21,259/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H7" s="22" t="inlineStr">
@@ -10773,7 +10773,7 @@
           <t>G | 222呎 (开放式)
 $498万
 $22,441/呎
-(26年-01月-15日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="I7" s="23" t="inlineStr">
@@ -10796,7 +10796,7 @@
           <t>A | 342呎 (1房)
 $682万
 $19,942/呎
-(25年-12月-16日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -10804,7 +10804,7 @@
           <t>B | 211呎 (开放式)
 $423万
 $20,062/呎
-(25年-03月-31日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -10812,7 +10812,7 @@
           <t>C | 220呎 (开放式)
 $404万
 $18,355/呎
-(25年-01月-26日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -10820,7 +10820,7 @@
           <t>D | 340呎 (1房)
 $784万
 $23,053/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -10828,7 +10828,7 @@
           <t>E | 324呎 (1房)
 $688万
 $21,241/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -10836,7 +10836,7 @@
           <t>F | 456呎 (2房)
 $946万
 $20,741/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
@@ -10844,7 +10844,7 @@
           <t>G | 222呎 (开放式)
 $454万
 $20,468/呎
-(25年-11月-20日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="I8" s="23" t="inlineStr">
@@ -10867,7 +10867,7 @@
           <t>A | 342呎 (1房)
 $665万
 $19,450/呎
-(25年-11月-13日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -10875,7 +10875,7 @@
           <t>B | 211呎 (开放式)
 $422万
 $20,000/呎
-(25年-01月-26日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -10883,7 +10883,7 @@
           <t>C | 220呎 (开放式)
 $398万
 $18,109/呎
-(25年-01月-26日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -10899,7 +10899,7 @@
           <t>E | 324呎 (1房)
 $679万
 $20,948/呎
-(25年-10月-15日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -10907,7 +10907,7 @@
           <t>F | 456呎 (2房)
 $934万
 $20,474/呎
-(26年-02月-09日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
@@ -10915,7 +10915,7 @@
           <t>G | 222呎 (开放式)
 $444万
 $20,018/呎
-(25年-12月-11日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -10923,7 +10923,7 @@
           <t>H | 283呎 (1房)
 $598万
 $21,117/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -10938,7 +10938,7 @@
           <t>A | 343呎 (1房)
 $656万
 $19,125/呎
-(25年-05月-14日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -10946,7 +10946,7 @@
           <t>B | 211呎 (开放式)
 $416万
 $19,697/呎
-(25年-02月-18日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -10954,7 +10954,7 @@
           <t>C | 220呎 (开放式)
 $393万
 $17,859/呎
-(25年-01月-26日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -10962,7 +10962,7 @@
           <t>D | 340呎 (1房)
 $698万
 $20,541/呎
-(25年-10月-23日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -10970,7 +10970,7 @@
           <t>E | 324呎 (1房)
 $691万
 $21,336/呎
-(25年-11月-06日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -10978,7 +10978,7 @@
           <t>F | 456呎 (2房)
 $920万
 $20,175/呎
-(26年-02月-02日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
@@ -10986,7 +10986,7 @@
           <t>G | 222呎 (开放式)
 $438万
 $19,743/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -10994,7 +10994,7 @@
           <t>H | 283呎 (1房)
 $589万
 $20,827/呎
-(25年-11月-17日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
           <t>A | 342呎 (1房)
 $654万
 $19,123/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -11017,7 +11017,7 @@
           <t>B | 211呎 (开放式)
 $410万
 $19,427/呎
-(25年-02月-09日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -11025,7 +11025,7 @@
           <t>C | 220呎 (开放式)
 $388万
 $17,618/呎
-(25年-01月-07日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -11033,7 +11033,7 @@
           <t>D | 340呎 (1房)
 $689万
 $20,259/呎
-(25年-11月-12日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -11041,7 +11041,7 @@
           <t>E | 324呎 (1房)
 $660万
 $20,367/呎
-(25年-10月-23日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -11049,7 +11049,7 @@
           <t>F | 456呎 (2房)
 $966万
 $21,189/呎
-(25年-10月-23日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -11057,7 +11057,7 @@
           <t>G | 222呎 (开放式)
 $441万
 $19,865/呎
-(25年-11月-27日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -11065,7 +11065,7 @@
           <t>H | 283呎 (1房)
 $581万
 $20,537/呎
-(25年-11月-11日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -11080,7 +11080,7 @@
           <t>A | 342呎 (1房)
 $638万
 $18,655/呎
-(25年-12月-10日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -11088,7 +11088,7 @@
           <t>B | 211呎 (开放式)
 $404万
 $19,161/呎
-(25年-02月-09日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -11096,7 +11096,7 @@
           <t>C | 220呎 (开放式)
 $402万
 $18,250/呎
-(25年-02月-24日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -11104,7 +11104,7 @@
           <t>D | 340呎 (1房)
 $679万
 $19,976/呎
-(25年-10月-30日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -11120,7 +11120,7 @@
           <t>F | 456呎 (2房)
 $954万
 $20,914/呎
-(25年-10月-13日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -11128,7 +11128,7 @@
           <t>G | 221呎 (开放式)
 $426万
 $19,299/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -11136,7 +11136,7 @@
           <t>H | 283呎 (1房)
 $573万
 $20,254/呎
-(25年-04月-06日)</t>
+(25年-04月)</t>
         </is>
       </c>
     </row>
@@ -11151,7 +11151,7 @@
           <t>A | 342呎 (1房)
 $629万
 $18,401/呎
-(25年-08月-28日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -11159,7 +11159,7 @@
           <t>B | 211呎 (开放式)
 $399万
 $18,900/呎
-(25年-02月-09日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -11167,7 +11167,7 @@
           <t>C | 220呎 (开放式)
 $377万
 $17,145/呎
-(25年-02月-06日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -11175,7 +11175,7 @@
           <t>D | 340呎 (1房)
 $670万
 $19,703/呎
-(25年-10月-29日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -11183,7 +11183,7 @@
           <t>E | 324呎 (1房)
 $642万
 $19,812/呎
-(25年-09月-25日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -11191,7 +11191,7 @@
           <t>F | 456呎 (2房)
 $941万
 $20,645/呎
-(25年-10月-15日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -11199,7 +11199,7 @@
           <t>G | 221呎 (开放式)
 $425万
 $19,213/呎
-(25年-07月-14日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
@@ -11207,7 +11207,7 @@
           <t>H | 283呎 (1房)
 $565万
 $19,972/呎
-(25年-10月-29日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -11222,7 +11222,7 @@
           <t>A | 343呎 (1房)
 $620万
 $18,090/呎
-(25年-02月-16日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -11230,7 +11230,7 @@
           <t>B | 211呎 (开放式)
 $394万
 $18,649/呎
-(25年-01月-26日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -11238,7 +11238,7 @@
           <t>C | 220呎 (开放式)
 $372万
 $16,918/呎
-(25年-01月-27日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -11246,7 +11246,7 @@
           <t>D | 340呎 (1房)
 $661万
 $19,432/呎
-(25年-08月-25日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -11254,7 +11254,7 @@
           <t>E | 324呎 (1房)
 $633万
 $19,540/呎
-(25年-07月-01日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -11262,7 +11262,7 @@
           <t>F | 456呎 (2房)
 $929万
 $20,382/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -11270,7 +11270,7 @@
           <t>G | 221呎 (开放式)
 $415万
 $18,783/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -11278,7 +11278,7 @@
           <t>H | 283呎 (1房)
 $557万
 $19,696/呎
-(25年-06月-07日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -11293,7 +11293,7 @@
           <t>A | 343呎 (1房)
 $612万
 $17,843/呎
-(25年-02月-04日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -11301,7 +11301,7 @@
           <t>B | 211呎 (开放式)
 $388万
 $18,393/呎
-(25年-02月-06日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -11309,7 +11309,7 @@
           <t>C | 220呎 (开放式)
 $367万
 $16,686/呎
-(25年-02月-04日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -11317,7 +11317,7 @@
           <t>D | 340呎 (1房)
 $652万
 $19,162/呎
-(25年-04月-10日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -11325,7 +11325,7 @@
           <t>E | 324呎 (1房)
 $624万
 $19,272/呎
-(25年-01月-23日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -11333,7 +11333,7 @@
           <t>F | 456呎 (2房)
 $918万
 $20,121/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -11341,7 +11341,7 @@
           <t>G | 221呎 (开放式)
 $413万
 $18,692/呎
-(25年-02月-09日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -11349,7 +11349,7 @@
           <t>H | 283呎 (1房)
 $550万
 $19,431/呎
-(25年-05月-13日)</t>
+(25年-05月)</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
           <t>A | 343呎 (1房)
 $604万
 $17,595/呎
-(25年-02月-04日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -11372,7 +11372,7 @@
           <t>B | 211呎 (开放式)
 $383万
 $18,137/呎
-(25年-02月-04日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -11380,7 +11380,7 @@
           <t>C | 220呎 (开放式)
 $362万
 $16,464/呎
-(25年-01月-27日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -11388,7 +11388,7 @@
           <t>D | 340呎 (1房)
 $643万
 $18,900/呎
-(25年-02月-16日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -11396,7 +11396,7 @@
           <t>E | 324呎 (1房)
 $616万
 $19,000/呎
-(25年-02月-10日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -11404,7 +11404,7 @@
           <t>F | 456呎 (2房)
 $922万
 $20,226/呎
-(25年-11月-03日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -11412,7 +11412,7 @@
           <t>G | 221呎 (开放式)
 $408万
 $18,443/呎
-(25年-05月-19日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -11420,7 +11420,7 @@
           <t>H | 283呎 (1房)
 $542万
 $19,159/呎
-(25年-06月-26日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -11435,7 +11435,7 @@
           <t>A | 343呎 (1房)
 $595万
 $17,353/呎
-(25年-02月-09日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -11443,7 +11443,7 @@
           <t>B | 211呎 (开放式)
 $374万
 $17,720/呎
-(25年-01月-27日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -11451,7 +11451,7 @@
           <t>C | 220呎 (开放式)
 $353万
 $16,064/呎
-(25年-01月-26日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -11459,7 +11459,7 @@
           <t>D | 340呎 (1房)
 $634万
 $18,632/呎
-(25年-01月-26日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -11467,7 +11467,7 @@
           <t>E | 324呎 (1房)
 $607万
 $18,741/呎
-(25年-02月-06日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -11475,7 +11475,7 @@
           <t>F | 456呎 (2房)
 $894万
 $19,607/呎
-(25年-06月-01日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -11483,7 +11483,7 @@
           <t>G | 221呎 (开放式)
 $398万
 $18,023/呎
-(25年-04月-06日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -11491,7 +11491,7 @@
           <t>H | 283呎 (1房)
 $535万
 $18,894/呎
-(25年-03月-31日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -11506,7 +11506,7 @@
           <t>A | 343呎 (1房)
 $587万
 $17,114/呎
-(25年-01月-23日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -11514,7 +11514,7 @@
           <t>B | 211呎 (开放式)
 $372万
 $17,654/呎
-(25年-01月-26日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -11522,7 +11522,7 @@
           <t>C | 220呎 (开放式)
 $352万
 $16,018/呎
-(25年-01月-26日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -11530,7 +11530,7 @@
           <t>D | 340呎 (1房)
 $652万
 $19,185/呎
-(25年-02月-17日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -11538,7 +11538,7 @@
           <t>E | 324呎 (1房)
 $599万
 $18,485/呎
-(25年-02月-03日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -11546,7 +11546,7 @@
           <t>F | 456呎 (2房)
 $883万
 $19,355/呎
-(25年-05月-01日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -11554,7 +11554,7 @@
           <t>G | 221呎 (开放式)
 $397万
 $17,950/呎
-(25年-02月-20日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -11562,7 +11562,7 @@
           <t>H | 283呎 (1房)
 $527万
 $18,633/呎
-(25年-01月-27日)</t>
+(25年-01月)</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
           <t>A | 343呎 (1房)
 $580万
 $16,895/呎
-(25年-02月-11日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -11585,7 +11585,7 @@
           <t>B | 211呎 (开放式)
 $368万
 $17,431/呎
-(25年-01月-23日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -11593,7 +11593,7 @@
           <t>C | 220呎 (开放式)
 $348万
 $15,818/呎
-(25年-01月-27日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -11601,7 +11601,7 @@
           <t>D | 340呎 (1房)
 $617万
 $18,144/呎
-(25年-01月-22日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -11609,7 +11609,7 @@
           <t>E | 324呎 (1房)
 $617万
 $19,046/呎
-(25年-02月-04日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -11617,7 +11617,7 @@
           <t>F | 456呎 (2房)
 $871万
 $19,105/呎
-(25年-08月-21日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -11625,7 +11625,7 @@
           <t>G | 221呎 (开放式)
 $392万
 $17,724/呎
-(25年-02月-26日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -11633,7 +11633,7 @@
           <t>H | 283呎 (1房)
 $521万
 $18,396/呎
-(25年-02月-02日)</t>
+(25年-02月)</t>
         </is>
       </c>
     </row>
@@ -11648,7 +11648,7 @@
           <t>A | 342呎 (1房)
 $597万
 $17,462/呎
-(25年-02月-02日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -11656,7 +11656,7 @@
           <t>B | 211呎 (开放式)
 $359万
 $17,033/呎
-(25年-01月-26日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -11664,7 +11664,7 @@
           <t>C | 220呎 (开放式)
 $340万
 $15,445/呎
-(25年-02月-09日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -11672,7 +11672,7 @@
           <t>D | 340呎 (1房)
 $609万
 $17,912/呎
-(25年-01月-23日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -11680,7 +11680,7 @@
           <t>E | 324呎 (1房)
 $584万
 $18,012/呎
-(25年-01月-26日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -11688,7 +11688,7 @@
           <t>F | 456呎 (2房)
 $860万
 $18,862/呎
-(25年-08月-05日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -11696,7 +11696,7 @@
           <t>G | 221呎 (开放式)
 $387万
 $17,507/呎
-(25年-01月-26日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -11704,7 +11704,7 @@
           <t>H | 283呎 (1房)
 $514万
 $18,163/呎
-(25年-03月-18日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -11719,7 +11719,7 @@
           <t>A | 342呎 (1房)
 $565万
 $16,512/呎
-(25年-02月-02日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -11727,7 +11727,7 @@
           <t>B | 211呎 (开放式)
 $349万
 $16,559/呎
-(25年-01月-26日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -11735,7 +11735,7 @@
           <t>C | 220呎 (开放式)
 $339万
 $15,418/呎
-(25年-01月-26日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -11743,7 +11743,7 @@
           <t>D | 340呎 (1房)
 $601万
 $17,679/呎
-(25年-02月-02日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -11751,7 +11751,7 @@
           <t>E | 324呎 (1房)
 $576万
 $17,778/呎
-(25年-01月-27日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -11759,7 +11759,7 @@
           <t>F | 456呎 (2房)
 $849万
 $18,618/呎
-(25年-07月-22日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -11767,7 +11767,7 @@
           <t>G | 221呎 (开放式)
 $382万
 $17,285/呎
-(25年-01月-26日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -11775,7 +11775,7 @@
           <t>H | 283呎 (1房)
 $507万
 $17,926/呎
-(25年-03月-13日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -11790,7 +11790,7 @@
           <t>A | 343呎 (1房)
 $548万
 $15,968/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -11798,7 +11798,7 @@
           <t>B | 211呎 (开放式)
 $341万
 $16,175/呎
-(25年-01月-26日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -11806,7 +11806,7 @@
           <t>C | 220呎 (开放式)
 $335万
 $15,232/呎
-(25年-02月-03日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -11814,7 +11814,7 @@
           <t>D | 340呎 (1房)
 $601万
 $17,682/呎
-(25年-02月-05日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -11822,7 +11822,7 @@
           <t>E | 324呎 (1房)
 $595万
 $18,358/呎
-(25年-01月-27日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -11830,7 +11830,7 @@
           <t>F | 456呎 (2房)
 $838万
 $18,382/呎
-(25年-05月-13日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -11838,7 +11838,7 @@
           <t>G | 221呎 (开放式)
 $377万
 $17,068/呎
-(25年-02月-11日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -11846,7 +11846,7 @@
           <t>H | 283呎 (1房)
 $517万
 $18,279/呎
-(25年-01月-26日)</t>
+(25年-01月)</t>
         </is>
       </c>
     </row>
@@ -11861,7 +11861,7 @@
           <t>A | 343呎 (1房)
 $548万
 $15,968/呎
-(25年-02月-03日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -11869,7 +11869,7 @@
           <t>B | 211呎 (开放式)
 $345万
 $16,355/呎
-(25年-02月-03日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -11877,7 +11877,7 @@
           <t>C | 220呎 (开放式)
 $335万
 $15,232/呎
-(25年-01月-26日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -11885,7 +11885,7 @@
           <t>D | 340呎 (1房)
 $595万
 $17,491/呎
-(25年-02月-12日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -11893,7 +11893,7 @@
           <t>E | 324呎 (1房)
 $570万
 $17,586/呎
-(25年-02月-09日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -11901,7 +11901,7 @@
           <t>F | 456呎 (2房)
 $838万
 $18,382/呎
-(25年-06月-17日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -11909,7 +11909,7 @@
           <t>G | 222呎 (开放式)
 $377万
 $16,991/呎
-(25年-02月-17日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -11917,7 +11917,7 @@
           <t>H | 283呎 (1房)
 $501万
 $17,696/呎
-(25年-02月-17日)</t>
+(25年-02月)</t>
         </is>
       </c>
     </row>
@@ -11932,7 +11932,7 @@
           <t>A | 305呎 (1房)
 $738万
 $24,203/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -11940,7 +11940,7 @@
           <t>B | 190呎 (开放式)
 $393万
 $20,674/呎
-(25年-05月-12日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -11948,7 +11948,7 @@
           <t>C | 197呎 (开放式)
 $378万
 $19,173/呎
-(25年-05月-13日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -11956,7 +11956,7 @@
           <t>D | 300呎 (1房)
 $679万
 $22,620/呎
-(25年-11月-27日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -11964,7 +11964,7 @@
           <t>E | 285呎 (1房)
 $646万
 $22,667/呎
-(25年-08月-21日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -11972,7 +11972,7 @@
           <t>F | 417呎 (2房)
 $1115万
 $26,739/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -11980,7 +11980,7 @@
           <t>G | 198呎 (开放式)
 $416万
 $20,985/呎
-(25年-05月-26日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -11988,7 +11988,7 @@
           <t>H | 246呎 (1房)
 $556万
 $22,585/呎
-(25年-05月-01日)</t>
+(25年-05月)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-筲箕湾-傲华.xlsx
+++ b/files/港岛-筲箕湾-傲华.xlsx
@@ -10654,7 +10654,7 @@
           <t>A | 343呎 (1房)
 $776万
 $22,630/呎
-(26年-06月)</t>
+(26年-06月-19日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -10662,7 +10662,7 @@
           <t>B | 211呎 (开放式)
 $444万
 $21,043/呎
-(25年-06月)</t>
+(25年-06月-01日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -10670,7 +10670,7 @@
           <t>C | 220呎 (开放式)
 $420万
 $19,082/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -10694,7 +10694,7 @@
           <t>F | 456呎 (2房)
 $975万
 $21,382/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
@@ -10702,7 +10702,7 @@
           <t>G | 222呎 (开放式)
 $485万
 $21,856/呎
-(26年-01月)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr">
@@ -10725,7 +10725,7 @@
           <t>A | 342呎 (1房)
 $756万
 $22,114/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -10733,7 +10733,7 @@
           <t>B | 211呎 (开放式)
 $434万
 $20,578/呎
-(25年-04月)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -10741,7 +10741,7 @@
           <t>C | 220呎 (开放式)
 $414万
 $18,823/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
@@ -10765,7 +10765,7 @@
           <t>F | 456呎 (2房)
 $969万
 $21,259/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="H7" s="22" t="inlineStr">
@@ -10773,7 +10773,7 @@
           <t>G | 222呎 (开放式)
 $498万
 $22,441/呎
-(26年-01月)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="I7" s="23" t="inlineStr">
@@ -10796,7 +10796,7 @@
           <t>A | 342呎 (1房)
 $682万
 $19,942/呎
-(25年-12月)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -10804,7 +10804,7 @@
           <t>B | 211呎 (开放式)
 $423万
 $20,062/呎
-(25年-03月)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -10812,7 +10812,7 @@
           <t>C | 220呎 (开放式)
 $404万
 $18,355/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -10820,7 +10820,7 @@
           <t>D | 340呎 (1房)
 $784万
 $23,053/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -10828,7 +10828,7 @@
           <t>E | 324呎 (1房)
 $688万
 $21,241/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -10836,7 +10836,7 @@
           <t>F | 456呎 (2房)
 $946万
 $20,741/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
@@ -10844,7 +10844,7 @@
           <t>G | 222呎 (开放式)
 $454万
 $20,468/呎
-(25年-11月)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="I8" s="23" t="inlineStr">
@@ -10867,7 +10867,7 @@
           <t>A | 342呎 (1房)
 $665万
 $19,450/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -10875,7 +10875,7 @@
           <t>B | 211呎 (开放式)
 $422万
 $20,000/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -10883,7 +10883,7 @@
           <t>C | 220呎 (开放式)
 $398万
 $18,109/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -10899,7 +10899,7 @@
           <t>E | 324呎 (1房)
 $679万
 $20,948/呎
-(25年-10月)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -10907,7 +10907,7 @@
           <t>F | 456呎 (2房)
 $934万
 $20,474/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
@@ -10915,7 +10915,7 @@
           <t>G | 222呎 (开放式)
 $444万
 $20,018/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -10923,7 +10923,7 @@
           <t>H | 283呎 (1房)
 $598万
 $21,117/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
     </row>
@@ -10938,7 +10938,7 @@
           <t>A | 343呎 (1房)
 $656万
 $19,125/呎
-(25年-05月)</t>
+(25年-05月-14日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -10946,7 +10946,7 @@
           <t>B | 211呎 (开放式)
 $416万
 $19,697/呎
-(25年-02月)</t>
+(25年-02月-18日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -10954,7 +10954,7 @@
           <t>C | 220呎 (开放式)
 $393万
 $17,859/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -10962,7 +10962,7 @@
           <t>D | 340呎 (1房)
 $698万
 $20,541/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -10970,7 +10970,7 @@
           <t>E | 324呎 (1房)
 $691万
 $21,336/呎
-(25年-11月)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -10978,7 +10978,7 @@
           <t>F | 456呎 (2房)
 $920万
 $20,175/呎
-(26年-02月)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
@@ -10986,7 +10986,7 @@
           <t>G | 222呎 (开放式)
 $438万
 $19,743/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -10994,7 +10994,7 @@
           <t>H | 283呎 (1房)
 $589万
 $20,827/呎
-(25年-11月)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
           <t>A | 342呎 (1房)
 $654万
 $19,123/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -11017,7 +11017,7 @@
           <t>B | 211呎 (开放式)
 $410万
 $19,427/呎
-(25年-02月)</t>
+(25年-02月-09日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -11025,7 +11025,7 @@
           <t>C | 220呎 (开放式)
 $388万
 $17,618/呎
-(25年-01月)</t>
+(25年-01月-07日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -11033,7 +11033,7 @@
           <t>D | 340呎 (1房)
 $689万
 $20,259/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -11041,7 +11041,7 @@
           <t>E | 324呎 (1房)
 $660万
 $20,367/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -11049,7 +11049,7 @@
           <t>F | 456呎 (2房)
 $966万
 $21,189/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -11057,7 +11057,7 @@
           <t>G | 222呎 (开放式)
 $441万
 $19,865/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -11065,7 +11065,7 @@
           <t>H | 283呎 (1房)
 $581万
 $20,537/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -11080,7 +11080,7 @@
           <t>A | 342呎 (1房)
 $638万
 $18,655/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -11088,7 +11088,7 @@
           <t>B | 211呎 (开放式)
 $404万
 $19,161/呎
-(25年-02月)</t>
+(25年-02月-09日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -11096,7 +11096,7 @@
           <t>C | 220呎 (开放式)
 $402万
 $18,250/呎
-(25年-02月)</t>
+(25年-02月-24日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -11104,7 +11104,7 @@
           <t>D | 340呎 (1房)
 $679万
 $19,976/呎
-(25年-10月)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -11120,7 +11120,7 @@
           <t>F | 456呎 (2房)
 $954万
 $20,914/呎
-(25年-10月)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -11128,7 +11128,7 @@
           <t>G | 221呎 (开放式)
 $426万
 $19,299/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -11136,7 +11136,7 @@
           <t>H | 283呎 (1房)
 $573万
 $20,254/呎
-(25年-04月)</t>
+(25年-04月-06日)</t>
         </is>
       </c>
     </row>
@@ -11151,7 +11151,7 @@
           <t>A | 342呎 (1房)
 $629万
 $18,401/呎
-(25年-08月)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -11159,7 +11159,7 @@
           <t>B | 211呎 (开放式)
 $399万
 $18,900/呎
-(25年-02月)</t>
+(25年-02月-09日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -11167,7 +11167,7 @@
           <t>C | 220呎 (开放式)
 $377万
 $17,145/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -11175,7 +11175,7 @@
           <t>D | 340呎 (1房)
 $670万
 $19,703/呎
-(25年-10月)</t>
+(25年-10月-29日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -11183,7 +11183,7 @@
           <t>E | 324呎 (1房)
 $642万
 $19,812/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -11191,7 +11191,7 @@
           <t>F | 456呎 (2房)
 $941万
 $20,645/呎
-(25年-10月)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -11199,7 +11199,7 @@
           <t>G | 221呎 (开放式)
 $425万
 $19,213/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
@@ -11207,7 +11207,7 @@
           <t>H | 283呎 (1房)
 $565万
 $19,972/呎
-(25年-10月)</t>
+(25年-10月-29日)</t>
         </is>
       </c>
     </row>
@@ -11222,7 +11222,7 @@
           <t>A | 343呎 (1房)
 $620万
 $18,090/呎
-(25年-02月)</t>
+(25年-02月-16日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -11230,7 +11230,7 @@
           <t>B | 211呎 (开放式)
 $394万
 $18,649/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -11238,7 +11238,7 @@
           <t>C | 220呎 (开放式)
 $372万
 $16,918/呎
-(25年-01月)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -11246,7 +11246,7 @@
           <t>D | 340呎 (1房)
 $661万
 $19,432/呎
-(25年-08月)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -11254,7 +11254,7 @@
           <t>E | 324呎 (1房)
 $633万
 $19,540/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -11262,7 +11262,7 @@
           <t>F | 456呎 (2房)
 $929万
 $20,382/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -11270,7 +11270,7 @@
           <t>G | 221呎 (开放式)
 $415万
 $18,783/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -11278,7 +11278,7 @@
           <t>H | 283呎 (1房)
 $557万
 $19,696/呎
-(25年-06月)</t>
+(25年-06月-07日)</t>
         </is>
       </c>
     </row>
@@ -11293,7 +11293,7 @@
           <t>A | 343呎 (1房)
 $612万
 $17,843/呎
-(25年-02月)</t>
+(25年-02月-04日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -11301,7 +11301,7 @@
           <t>B | 211呎 (开放式)
 $388万
 $18,393/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -11309,7 +11309,7 @@
           <t>C | 220呎 (开放式)
 $367万
 $16,686/呎
-(25年-02月)</t>
+(25年-02月-04日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -11317,7 +11317,7 @@
           <t>D | 340呎 (1房)
 $652万
 $19,162/呎
-(25年-04月)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -11325,7 +11325,7 @@
           <t>E | 324呎 (1房)
 $624万
 $19,272/呎
-(25年-01月)</t>
+(25年-01月-23日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -11333,7 +11333,7 @@
           <t>F | 456呎 (2房)
 $918万
 $20,121/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -11341,7 +11341,7 @@
           <t>G | 221呎 (开放式)
 $413万
 $18,692/呎
-(25年-02月)</t>
+(25年-02月-09日)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -11349,7 +11349,7 @@
           <t>H | 283呎 (1房)
 $550万
 $19,431/呎
-(25年-05月)</t>
+(25年-05月-13日)</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
           <t>A | 343呎 (1房)
 $604万
 $17,595/呎
-(25年-02月)</t>
+(25年-02月-04日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -11372,7 +11372,7 @@
           <t>B | 211呎 (开放式)
 $383万
 $18,137/呎
-(25年-02月)</t>
+(25年-02月-04日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -11380,7 +11380,7 @@
           <t>C | 220呎 (开放式)
 $362万
 $16,464/呎
-(25年-01月)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -11388,7 +11388,7 @@
           <t>D | 340呎 (1房)
 $643万
 $18,900/呎
-(25年-02月)</t>
+(25年-02月-16日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -11396,7 +11396,7 @@
           <t>E | 324呎 (1房)
 $616万
 $19,000/呎
-(25年-02月)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -11404,7 +11404,7 @@
           <t>F | 456呎 (2房)
 $922万
 $20,226/呎
-(25年-11月)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -11412,7 +11412,7 @@
           <t>G | 221呎 (开放式)
 $408万
 $18,443/呎
-(25年-05月)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -11420,7 +11420,7 @@
           <t>H | 283呎 (1房)
 $542万
 $19,159/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
     </row>
@@ -11435,7 +11435,7 @@
           <t>A | 343呎 (1房)
 $595万
 $17,353/呎
-(25年-02月)</t>
+(25年-02月-09日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -11443,7 +11443,7 @@
           <t>B | 211呎 (开放式)
 $374万
 $17,720/呎
-(25年-01月)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -11451,7 +11451,7 @@
           <t>C | 220呎 (开放式)
 $353万
 $16,064/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -11459,7 +11459,7 @@
           <t>D | 340呎 (1房)
 $634万
 $18,632/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -11467,7 +11467,7 @@
           <t>E | 324呎 (1房)
 $607万
 $18,741/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -11475,7 +11475,7 @@
           <t>F | 456呎 (2房)
 $894万
 $19,607/呎
-(25年-06月)</t>
+(25年-06月-01日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -11483,7 +11483,7 @@
           <t>G | 221呎 (开放式)
 $398万
 $18,023/呎
-(25年-04月)</t>
+(25年-04月-06日)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -11491,7 +11491,7 @@
           <t>H | 283呎 (1房)
 $535万
 $18,894/呎
-(25年-03月)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
     </row>
@@ -11506,7 +11506,7 @@
           <t>A | 343呎 (1房)
 $587万
 $17,114/呎
-(25年-01月)</t>
+(25年-01月-23日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -11514,7 +11514,7 @@
           <t>B | 211呎 (开放式)
 $372万
 $17,654/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -11522,7 +11522,7 @@
           <t>C | 220呎 (开放式)
 $352万
 $16,018/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -11530,7 +11530,7 @@
           <t>D | 340呎 (1房)
 $652万
 $19,185/呎
-(25年-02月)</t>
+(25年-02月-17日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -11538,7 +11538,7 @@
           <t>E | 324呎 (1房)
 $599万
 $18,485/呎
-(25年-02月)</t>
+(25年-02月-03日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -11546,7 +11546,7 @@
           <t>F | 456呎 (2房)
 $883万
 $19,355/呎
-(25年-05月)</t>
+(25年-05月-01日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -11554,7 +11554,7 @@
           <t>G | 221呎 (开放式)
 $397万
 $17,950/呎
-(25年-02月)</t>
+(25年-02月-20日)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -11562,7 +11562,7 @@
           <t>H | 283呎 (1房)
 $527万
 $18,633/呎
-(25年-01月)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
           <t>A | 343呎 (1房)
 $580万
 $16,895/呎
-(25年-02月)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -11585,7 +11585,7 @@
           <t>B | 211呎 (开放式)
 $368万
 $17,431/呎
-(25年-01月)</t>
+(25年-01月-23日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -11593,7 +11593,7 @@
           <t>C | 220呎 (开放式)
 $348万
 $15,818/呎
-(25年-01月)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -11601,7 +11601,7 @@
           <t>D | 340呎 (1房)
 $617万
 $18,144/呎
-(25年-01月)</t>
+(25年-01月-22日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -11609,7 +11609,7 @@
           <t>E | 324呎 (1房)
 $617万
 $19,046/呎
-(25年-02月)</t>
+(25年-02月-04日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -11617,7 +11617,7 @@
           <t>F | 456呎 (2房)
 $871万
 $19,105/呎
-(25年-08月)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -11625,7 +11625,7 @@
           <t>G | 221呎 (开放式)
 $392万
 $17,724/呎
-(25年-02月)</t>
+(25年-02月-26日)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -11633,7 +11633,7 @@
           <t>H | 283呎 (1房)
 $521万
 $18,396/呎
-(25年-02月)</t>
+(25年-02月-02日)</t>
         </is>
       </c>
     </row>
@@ -11648,7 +11648,7 @@
           <t>A | 342呎 (1房)
 $597万
 $17,462/呎
-(25年-02月)</t>
+(25年-02月-02日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -11656,7 +11656,7 @@
           <t>B | 211呎 (开放式)
 $359万
 $17,033/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -11664,7 +11664,7 @@
           <t>C | 220呎 (开放式)
 $340万
 $15,445/呎
-(25年-02月)</t>
+(25年-02月-09日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -11672,7 +11672,7 @@
           <t>D | 340呎 (1房)
 $609万
 $17,912/呎
-(25年-01月)</t>
+(25年-01月-23日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -11680,7 +11680,7 @@
           <t>E | 324呎 (1房)
 $584万
 $18,012/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -11688,7 +11688,7 @@
           <t>F | 456呎 (2房)
 $860万
 $18,862/呎
-(25年-08月)</t>
+(25年-08月-05日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -11696,7 +11696,7 @@
           <t>G | 221呎 (开放式)
 $387万
 $17,507/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -11704,7 +11704,7 @@
           <t>H | 283呎 (1房)
 $514万
 $18,163/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
     </row>
@@ -11719,7 +11719,7 @@
           <t>A | 342呎 (1房)
 $565万
 $16,512/呎
-(25年-02月)</t>
+(25年-02月-02日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -11727,7 +11727,7 @@
           <t>B | 211呎 (开放式)
 $349万
 $16,559/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -11735,7 +11735,7 @@
           <t>C | 220呎 (开放式)
 $339万
 $15,418/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -11743,7 +11743,7 @@
           <t>D | 340呎 (1房)
 $601万
 $17,679/呎
-(25年-02月)</t>
+(25年-02月-02日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -11751,7 +11751,7 @@
           <t>E | 324呎 (1房)
 $576万
 $17,778/呎
-(25年-01月)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -11759,7 +11759,7 @@
           <t>F | 456呎 (2房)
 $849万
 $18,618/呎
-(25年-07月)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -11767,7 +11767,7 @@
           <t>G | 221呎 (开放式)
 $382万
 $17,285/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -11775,7 +11775,7 @@
           <t>H | 283呎 (1房)
 $507万
 $17,926/呎
-(25年-03月)</t>
+(25年-03月-13日)</t>
         </is>
       </c>
     </row>
@@ -11790,7 +11790,7 @@
           <t>A | 343呎 (1房)
 $548万
 $15,968/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -11798,7 +11798,7 @@
           <t>B | 211呎 (开放式)
 $341万
 $16,175/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -11806,7 +11806,7 @@
           <t>C | 220呎 (开放式)
 $335万
 $15,232/呎
-(25年-02月)</t>
+(25年-02月-03日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -11814,7 +11814,7 @@
           <t>D | 340呎 (1房)
 $601万
 $17,682/呎
-(25年-02月)</t>
+(25年-02月-05日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -11822,7 +11822,7 @@
           <t>E | 324呎 (1房)
 $595万
 $18,358/呎
-(25年-01月)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -11830,7 +11830,7 @@
           <t>F | 456呎 (2房)
 $838万
 $18,382/呎
-(25年-05月)</t>
+(25年-05月-13日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -11838,7 +11838,7 @@
           <t>G | 221呎 (开放式)
 $377万
 $17,068/呎
-(25年-02月)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -11846,7 +11846,7 @@
           <t>H | 283呎 (1房)
 $517万
 $18,279/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
     </row>
@@ -11861,7 +11861,7 @@
           <t>A | 343呎 (1房)
 $548万
 $15,968/呎
-(25年-02月)</t>
+(25年-02月-03日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -11869,7 +11869,7 @@
           <t>B | 211呎 (开放式)
 $345万
 $16,355/呎
-(25年-02月)</t>
+(25年-02月-03日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -11877,7 +11877,7 @@
           <t>C | 220呎 (开放式)
 $335万
 $15,232/呎
-(25年-01月)</t>
+(25年-01月-26日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -11885,7 +11885,7 @@
           <t>D | 340呎 (1房)
 $595万
 $17,491/呎
-(25年-02月)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -11893,7 +11893,7 @@
           <t>E | 324呎 (1房)
 $570万
 $17,586/呎
-(25年-02月)</t>
+(25年-02月-09日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -11901,7 +11901,7 @@
           <t>F | 456呎 (2房)
 $838万
 $18,382/呎
-(25年-06月)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -11909,7 +11909,7 @@
           <t>G | 222呎 (开放式)
 $377万
 $16,991/呎
-(25年-02月)</t>
+(25年-02月-17日)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -11917,7 +11917,7 @@
           <t>H | 283呎 (1房)
 $501万
 $17,696/呎
-(25年-02月)</t>
+(25年-02月-17日)</t>
         </is>
       </c>
     </row>
@@ -11932,7 +11932,7 @@
           <t>A | 305呎 (1房)
 $738万
 $24,203/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -11940,7 +11940,7 @@
           <t>B | 190呎 (开放式)
 $393万
 $20,674/呎
-(25年-05月)</t>
+(25年-05月-12日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -11948,7 +11948,7 @@
           <t>C | 197呎 (开放式)
 $378万
 $19,173/呎
-(25年-05月)</t>
+(25年-05月-13日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -11956,7 +11956,7 @@
           <t>D | 300呎 (1房)
 $679万
 $22,620/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -11964,7 +11964,7 @@
           <t>E | 285呎 (1房)
 $646万
 $22,667/呎
-(25年-08月)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -11972,7 +11972,7 @@
           <t>F | 417呎 (2房)
 $1115万
 $26,739/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -11980,7 +11980,7 @@
           <t>G | 198呎 (开放式)
 $416万
 $20,985/呎
-(25年-05月)</t>
+(25年-05月-26日)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -11988,7 +11988,7 @@
           <t>H | 246呎 (1房)
 $556万
 $22,585/呎
-(25年-05月)</t>
+(25年-05月-01日)</t>
         </is>
       </c>
     </row>
